--- a/LangMod/EN/SmallResource.xlsx
+++ b/LangMod/EN/SmallResource.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="143">
   <si>
     <t>id</t>
   </si>
@@ -66,7 +66,7 @@
     <t>15</t>
   </si>
   <si>
-    <t>6491001</t>
+    <t>6491011</t>
   </si>
   <si>
     <t>SawMill</t>
@@ -78,286 +78,328 @@
     <t>plank</t>
   </si>
   <si>
+    <t>log_small</t>
+  </si>
+  <si>
+    <t>known</t>
+  </si>
+  <si>
+    <t>6491012</t>
+  </si>
+  <si>
+    <t>StoneCutter</t>
+  </si>
+  <si>
+    <t>cutstone</t>
+  </si>
+  <si>
+    <t>rock_small</t>
+  </si>
+  <si>
+    <t>6491013</t>
+  </si>
+  <si>
+    <t>Kiln</t>
+  </si>
+  <si>
+    <t>brick</t>
+  </si>
+  <si>
+    <t>clay_small</t>
+  </si>
+  <si>
+    <t>6491014</t>
+  </si>
+  <si>
+    <t>glass</t>
+  </si>
+  <si>
+    <t>fragment_small</t>
+  </si>
+  <si>
+    <t>name_JP</t>
+  </si>
+  <si>
+    <t>unknown_JP</t>
+  </si>
+  <si>
+    <t>unit_JP</t>
+  </si>
+  <si>
+    <t>naming</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>unit</t>
+  </si>
+  <si>
+    <t>unknown</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>sort</t>
+  </si>
+  <si>
+    <t>_tileType</t>
+  </si>
+  <si>
+    <t>_idRenderData</t>
+  </si>
+  <si>
+    <t>tiles</t>
+  </si>
+  <si>
+    <t>altTiles</t>
+  </si>
+  <si>
+    <t>anime</t>
+  </si>
+  <si>
+    <t>skins</t>
+  </si>
+  <si>
+    <t>size</t>
+  </si>
+  <si>
+    <t>colorMod</t>
+  </si>
+  <si>
+    <t>colorType</t>
+  </si>
+  <si>
+    <t>recipeKey</t>
+  </si>
+  <si>
+    <t>components</t>
+  </si>
+  <si>
+    <t>disassemble</t>
+  </si>
+  <si>
+    <t>defMat</t>
+  </si>
+  <si>
+    <t>tierGroup</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>LV</t>
+  </si>
+  <si>
+    <t>chance</t>
+  </si>
+  <si>
+    <t>quality</t>
+  </si>
+  <si>
+    <t>HP</t>
+  </si>
+  <si>
+    <t>weight</t>
+  </si>
+  <si>
+    <t>electricity</t>
+  </si>
+  <si>
+    <t>trait</t>
+  </si>
+  <si>
+    <t>elements</t>
+  </si>
+  <si>
+    <t>range</t>
+  </si>
+  <si>
+    <t>attackType</t>
+  </si>
+  <si>
+    <t>offense</t>
+  </si>
+  <si>
+    <t>substats</t>
+  </si>
+  <si>
+    <t>defense</t>
+  </si>
+  <si>
+    <t>lightData</t>
+  </si>
+  <si>
+    <t>idExtra</t>
+  </si>
+  <si>
+    <t>idToggleExtra</t>
+  </si>
+  <si>
+    <t>idActorEx</t>
+  </si>
+  <si>
+    <t>idSound</t>
+  </si>
+  <si>
+    <t>workTag</t>
+  </si>
+  <si>
+    <t>filter</t>
+  </si>
+  <si>
+    <t>roomName_JP</t>
+  </si>
+  <si>
+    <t>roomName</t>
+  </si>
+  <si>
+    <t>detail_JP</t>
+  </si>
+  <si>
+    <t>detail</t>
+  </si>
+  <si>
+    <t>int[]</t>
+  </si>
+  <si>
+    <t>個</t>
+  </si>
+  <si>
+    <t>other</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>log</t>
+  </si>
+  <si>
+    <t>oak</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>小さな丸太</t>
+  </si>
+  <si>
+    <t>本</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>small log</t>
+  </si>
+  <si>
+    <t>wood</t>
+  </si>
+  <si>
+    <t>resource_wood</t>
+  </si>
+  <si>
+    <t>@obj_S</t>
+  </si>
+  <si>
+    <t>branch/2</t>
+  </si>
+  <si>
+    <t>ResourceMain</t>
+  </si>
+  <si>
+    <t>小さな粘土</t>
+  </si>
+  <si>
+    <t>small clay</t>
+  </si>
+  <si>
+    <t>_resource</t>
+  </si>
+  <si>
+    <t>resource_soil</t>
+  </si>
+  <si>
+    <t>@obj_S flat</t>
+  </si>
+  <si>
+    <t>chunk</t>
+  </si>
+  <si>
+    <t>mud</t>
+  </si>
+  <si>
+    <t>小さな欠片</t>
+  </si>
+  <si>
+    <t>small fragment</t>
+  </si>
+  <si>
+    <t>resource_fragment</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>小さな石</t>
+  </si>
+  <si>
+    <t>small stone</t>
+  </si>
+  <si>
+    <t>stone</t>
+  </si>
+  <si>
+    <t>resource_stone</t>
+  </si>
+  <si>
+    <t>pebble/2</t>
+  </si>
+  <si>
+    <t>granite</t>
+  </si>
+  <si>
+    <t>※このアイテムは将来のアプデで無効化されます。加工する事で有効なアイテムに変換できます。</t>
+  </si>
+  <si>
+    <t>*This item will be disabled in a future update. You can convert it into a usable item by processing it.</t>
+  </si>
+  <si>
     <t>logSmall</t>
   </si>
   <si>
-    <t>known</t>
-  </si>
-  <si>
-    <t>6491002</t>
-  </si>
-  <si>
-    <t>StoneCutter</t>
-  </si>
-  <si>
-    <t>cutstone</t>
+    <t>小さな丸太(Old)</t>
+  </si>
+  <si>
+    <t>small log(Old)</t>
+  </si>
+  <si>
+    <t>claySmall</t>
+  </si>
+  <si>
+    <t>小さな粘土(Old)</t>
+  </si>
+  <si>
+    <t>small clay(Old)</t>
+  </si>
+  <si>
+    <t>fragmentSmall</t>
+  </si>
+  <si>
+    <t>小さな欠片(Old)</t>
+  </si>
+  <si>
+    <t>small fragment(Old)</t>
   </si>
   <si>
     <t>rockSmall</t>
   </si>
   <si>
-    <t>6491003</t>
-  </si>
-  <si>
-    <t>Kiln</t>
-  </si>
-  <si>
-    <t>brick</t>
-  </si>
-  <si>
-    <t>claySmall</t>
-  </si>
-  <si>
-    <t>6491004</t>
-  </si>
-  <si>
-    <t>glass</t>
-  </si>
-  <si>
-    <t>fragmentSmall</t>
-  </si>
-  <si>
-    <t>name_JP</t>
-  </si>
-  <si>
-    <t>unknown_JP</t>
-  </si>
-  <si>
-    <t>unit_JP</t>
-  </si>
-  <si>
-    <t>naming</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>unit</t>
-  </si>
-  <si>
-    <t>unknown</t>
-  </si>
-  <si>
-    <t>category</t>
-  </si>
-  <si>
-    <t>sort</t>
-  </si>
-  <si>
-    <t>_tileType</t>
-  </si>
-  <si>
-    <t>_idRenderData</t>
-  </si>
-  <si>
-    <t>tiles</t>
-  </si>
-  <si>
-    <t>altTiles</t>
-  </si>
-  <si>
-    <t>anime</t>
-  </si>
-  <si>
-    <t>skins</t>
-  </si>
-  <si>
-    <t>size</t>
-  </si>
-  <si>
-    <t>colorMod</t>
-  </si>
-  <si>
-    <t>colorType</t>
-  </si>
-  <si>
-    <t>recipeKey</t>
-  </si>
-  <si>
-    <t>components</t>
-  </si>
-  <si>
-    <t>disassemble</t>
-  </si>
-  <si>
-    <t>defMat</t>
-  </si>
-  <si>
-    <t>tierGroup</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>LV</t>
-  </si>
-  <si>
-    <t>chance</t>
-  </si>
-  <si>
-    <t>quality</t>
-  </si>
-  <si>
-    <t>HP</t>
-  </si>
-  <si>
-    <t>weight</t>
-  </si>
-  <si>
-    <t>electricity</t>
-  </si>
-  <si>
-    <t>trait</t>
-  </si>
-  <si>
-    <t>elements</t>
-  </si>
-  <si>
-    <t>range</t>
-  </si>
-  <si>
-    <t>attackType</t>
-  </si>
-  <si>
-    <t>offense</t>
-  </si>
-  <si>
-    <t>substats</t>
-  </si>
-  <si>
-    <t>defense</t>
-  </si>
-  <si>
-    <t>lightData</t>
-  </si>
-  <si>
-    <t>idExtra</t>
-  </si>
-  <si>
-    <t>idToggleExtra</t>
-  </si>
-  <si>
-    <t>idActorEx</t>
-  </si>
-  <si>
-    <t>idSound</t>
-  </si>
-  <si>
-    <t>workTag</t>
-  </si>
-  <si>
-    <t>filter</t>
-  </si>
-  <si>
-    <t>roomName_JP</t>
-  </si>
-  <si>
-    <t>roomName</t>
-  </si>
-  <si>
-    <t>detail_JP</t>
-  </si>
-  <si>
-    <t>detail</t>
-  </si>
-  <si>
-    <t>int[]</t>
-  </si>
-  <si>
-    <t>個</t>
-  </si>
-  <si>
-    <t>other</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>log</t>
-  </si>
-  <si>
-    <t>oak</t>
-  </si>
-  <si>
-    <t>1000</t>
-  </si>
-  <si>
-    <t>小さな丸太</t>
-  </si>
-  <si>
-    <t>本</t>
-  </si>
-  <si>
-    <t>m</t>
-  </si>
-  <si>
-    <t>small log</t>
-  </si>
-  <si>
-    <t>wood</t>
-  </si>
-  <si>
-    <t>resource_wood</t>
-  </si>
-  <si>
-    <t>@obj_S</t>
-  </si>
-  <si>
-    <t>branch/2</t>
-  </si>
-  <si>
-    <t>ResourceMain</t>
-  </si>
-  <si>
-    <t>小さな粘土</t>
-  </si>
-  <si>
-    <t>small clay</t>
-  </si>
-  <si>
-    <t>_resource</t>
-  </si>
-  <si>
-    <t>resource_soil</t>
-  </si>
-  <si>
-    <t>@obj_S flat</t>
-  </si>
-  <si>
-    <t>chunk</t>
-  </si>
-  <si>
-    <t>mud</t>
-  </si>
-  <si>
-    <t>小さな欠片</t>
-  </si>
-  <si>
-    <t>small fragment</t>
-  </si>
-  <si>
-    <t>resource_fragment</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>小さな石</t>
-  </si>
-  <si>
-    <t>small stone</t>
-  </si>
-  <si>
-    <t>stone</t>
-  </si>
-  <si>
-    <t>resource_stone</t>
-  </si>
-  <si>
-    <t>pebble/2</t>
-  </si>
-  <si>
-    <t>granite</t>
+    <t>小さな石(Old)</t>
+  </si>
+  <si>
+    <t>small stone(Old)</t>
   </si>
   <si>
     <t>Tes</t>
@@ -1134,7 +1176,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="9.75"/>
+    <col customWidth="1" min="2" max="2" width="15.88"/>
     <col customWidth="1" min="3" max="3" width="4.88"/>
     <col customWidth="1" min="4" max="4" width="6.38"/>
     <col customWidth="1" min="5" max="5" width="2.88"/>
@@ -1178,8 +1220,8 @@
     <col customWidth="1" min="47" max="47" width="7.25"/>
     <col customWidth="1" min="48" max="49" width="6.0"/>
     <col customWidth="1" min="50" max="50" width="9.0"/>
-    <col customWidth="1" min="51" max="51" width="7.63"/>
-    <col customWidth="1" min="52" max="52" width="5.0"/>
+    <col customWidth="1" min="51" max="51" width="73.63"/>
+    <col customWidth="1" min="52" max="52" width="48.25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2013,8 +2055,12 @@
       <c r="AV7" s="1"/>
       <c r="AW7" s="3"/>
       <c r="AX7" s="3"/>
-      <c r="AY7" s="3"/>
-      <c r="AZ7" s="3"/>
+      <c r="AY7" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="AZ7" s="9" t="s">
+        <v>116</v>
+      </c>
       <c r="BA7" s="3"/>
       <c r="BB7" s="3"/>
       <c r="BC7" s="3"/>
@@ -2036,6 +2082,418 @@
       <c r="BS7" s="3"/>
       <c r="BT7" s="3"/>
     </row>
+    <row r="8">
+      <c r="A8" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="N8" s="10"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="3"/>
+      <c r="S8" s="3"/>
+      <c r="T8" s="3"/>
+      <c r="U8" s="3"/>
+      <c r="V8" s="3"/>
+      <c r="W8" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="X8" s="3"/>
+      <c r="Y8" s="3"/>
+      <c r="Z8" s="3"/>
+      <c r="AA8" s="14">
+        <v>30.0</v>
+      </c>
+      <c r="AB8" s="15">
+        <v>1.0</v>
+      </c>
+      <c r="AC8" s="3"/>
+      <c r="AD8" s="3"/>
+      <c r="AE8" s="3"/>
+      <c r="AF8" s="14">
+        <v>600.0</v>
+      </c>
+      <c r="AG8" s="3"/>
+      <c r="AH8" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="AI8" s="3"/>
+      <c r="AJ8" s="3"/>
+      <c r="AK8" s="3"/>
+      <c r="AL8" s="3"/>
+      <c r="AM8" s="3"/>
+      <c r="AN8" s="3"/>
+      <c r="AO8" s="3"/>
+      <c r="AP8" s="3"/>
+      <c r="AQ8" s="3"/>
+      <c r="AR8" s="3"/>
+      <c r="AS8" s="3"/>
+      <c r="AT8" s="3"/>
+      <c r="AU8" s="3"/>
+      <c r="AV8" s="1"/>
+      <c r="AW8" s="3"/>
+      <c r="AX8" s="3"/>
+      <c r="AY8" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="AZ8" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="BA8" s="3"/>
+      <c r="BB8" s="3"/>
+      <c r="BC8" s="3"/>
+      <c r="BD8" s="3"/>
+      <c r="BE8" s="3"/>
+      <c r="BF8" s="3"/>
+      <c r="BG8" s="3"/>
+      <c r="BH8" s="3"/>
+      <c r="BI8" s="3"/>
+      <c r="BJ8" s="3"/>
+      <c r="BK8" s="3"/>
+      <c r="BL8" s="3"/>
+      <c r="BM8" s="3"/>
+      <c r="BN8" s="3"/>
+      <c r="BO8" s="3"/>
+      <c r="BP8" s="3"/>
+      <c r="BQ8" s="3"/>
+      <c r="BR8" s="3"/>
+      <c r="BS8" s="3"/>
+      <c r="BT8" s="3"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="N9" s="10"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3"/>
+      <c r="S9" s="3"/>
+      <c r="T9" s="3"/>
+      <c r="U9" s="3"/>
+      <c r="V9" s="3"/>
+      <c r="W9" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="X9" s="3"/>
+      <c r="Y9" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z9" s="3"/>
+      <c r="AA9" s="14">
+        <v>70.0</v>
+      </c>
+      <c r="AB9" s="15">
+        <v>4.0</v>
+      </c>
+      <c r="AC9" s="3"/>
+      <c r="AD9" s="3"/>
+      <c r="AE9" s="3"/>
+      <c r="AF9" s="14">
+        <v>90.0</v>
+      </c>
+      <c r="AG9" s="3"/>
+      <c r="AH9" s="3"/>
+      <c r="AI9" s="3"/>
+      <c r="AJ9" s="3"/>
+      <c r="AK9" s="3"/>
+      <c r="AL9" s="3"/>
+      <c r="AM9" s="3"/>
+      <c r="AN9" s="3"/>
+      <c r="AO9" s="3"/>
+      <c r="AP9" s="3"/>
+      <c r="AQ9" s="3"/>
+      <c r="AR9" s="3"/>
+      <c r="AS9" s="3"/>
+      <c r="AT9" s="3"/>
+      <c r="AU9" s="3"/>
+      <c r="AV9" s="1"/>
+      <c r="AW9" s="3"/>
+      <c r="AX9" s="3"/>
+      <c r="AY9" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="AZ9" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="BA9" s="3"/>
+      <c r="BB9" s="3"/>
+      <c r="BC9" s="3"/>
+      <c r="BD9" s="3"/>
+      <c r="BE9" s="3"/>
+      <c r="BF9" s="3"/>
+      <c r="BG9" s="3"/>
+      <c r="BH9" s="3"/>
+      <c r="BI9" s="3"/>
+      <c r="BJ9" s="3"/>
+      <c r="BK9" s="3"/>
+      <c r="BL9" s="3"/>
+      <c r="BM9" s="3"/>
+      <c r="BN9" s="3"/>
+      <c r="BO9" s="3"/>
+      <c r="BP9" s="3"/>
+      <c r="BQ9" s="3"/>
+      <c r="BR9" s="3"/>
+      <c r="BS9" s="3"/>
+      <c r="BT9" s="3"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="N10" s="10"/>
+      <c r="O10" s="3"/>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="3"/>
+      <c r="R10" s="3"/>
+      <c r="S10" s="3"/>
+      <c r="T10" s="3"/>
+      <c r="U10" s="3"/>
+      <c r="V10" s="3"/>
+      <c r="W10" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="X10" s="3"/>
+      <c r="Y10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z10" s="3"/>
+      <c r="AA10" s="14">
+        <v>10.0</v>
+      </c>
+      <c r="AB10" s="15">
+        <v>1.0</v>
+      </c>
+      <c r="AC10" s="3"/>
+      <c r="AD10" s="3"/>
+      <c r="AE10" s="3"/>
+      <c r="AF10" s="14">
+        <v>60.0</v>
+      </c>
+      <c r="AG10" s="3"/>
+      <c r="AH10" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="AI10" s="3"/>
+      <c r="AJ10" s="3"/>
+      <c r="AK10" s="3"/>
+      <c r="AL10" s="3"/>
+      <c r="AM10" s="3"/>
+      <c r="AN10" s="3"/>
+      <c r="AO10" s="3"/>
+      <c r="AP10" s="3"/>
+      <c r="AQ10" s="3"/>
+      <c r="AR10" s="3"/>
+      <c r="AS10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AT10" s="3"/>
+      <c r="AU10" s="3"/>
+      <c r="AV10" s="1"/>
+      <c r="AW10" s="3"/>
+      <c r="AX10" s="3"/>
+      <c r="AY10" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="AZ10" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="BA10" s="3"/>
+      <c r="BB10" s="3"/>
+      <c r="BC10" s="3"/>
+      <c r="BD10" s="3"/>
+      <c r="BE10" s="3"/>
+      <c r="BF10" s="3"/>
+      <c r="BG10" s="3"/>
+      <c r="BH10" s="3"/>
+      <c r="BI10" s="3"/>
+      <c r="BJ10" s="3"/>
+      <c r="BK10" s="3"/>
+      <c r="BL10" s="3"/>
+      <c r="BM10" s="3"/>
+      <c r="BN10" s="3"/>
+      <c r="BO10" s="3"/>
+      <c r="BP10" s="3"/>
+      <c r="BQ10" s="3"/>
+      <c r="BR10" s="3"/>
+      <c r="BS10" s="3"/>
+      <c r="BT10" s="3"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="N11" s="1"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+      <c r="U11" s="3"/>
+      <c r="V11" s="3"/>
+      <c r="W11" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="X11" s="3"/>
+      <c r="Y11" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z11" s="3"/>
+      <c r="AA11" s="14">
+        <v>25.0</v>
+      </c>
+      <c r="AB11" s="15">
+        <v>1.0</v>
+      </c>
+      <c r="AC11" s="3"/>
+      <c r="AD11" s="3"/>
+      <c r="AE11" s="3"/>
+      <c r="AF11" s="14">
+        <v>500.0</v>
+      </c>
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
+      <c r="AR11" s="3"/>
+      <c r="AS11" s="3"/>
+      <c r="AT11" s="3"/>
+      <c r="AU11" s="3"/>
+      <c r="AV11" s="1"/>
+      <c r="AW11" s="3"/>
+      <c r="AX11" s="3"/>
+      <c r="AY11" s="3"/>
+      <c r="AZ11" s="3"/>
+      <c r="BA11" s="3"/>
+      <c r="BB11" s="3"/>
+      <c r="BC11" s="3"/>
+      <c r="BD11" s="3"/>
+      <c r="BE11" s="3"/>
+      <c r="BF11" s="3"/>
+      <c r="BG11" s="3"/>
+      <c r="BH11" s="3"/>
+      <c r="BI11" s="3"/>
+      <c r="BJ11" s="3"/>
+      <c r="BK11" s="3"/>
+      <c r="BL11" s="3"/>
+      <c r="BM11" s="3"/>
+      <c r="BN11" s="3"/>
+      <c r="BO11" s="3"/>
+      <c r="BP11" s="3"/>
+      <c r="BQ11" s="3"/>
+      <c r="BR11" s="3"/>
+      <c r="BS11" s="3"/>
+      <c r="BT11" s="3"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -2050,15 +2508,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="16" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3" t="s">
@@ -2066,23 +2524,23 @@
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="1" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="1" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="1" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
@@ -2091,13 +2549,13 @@
       <c r="S4" s="3"/>
       <c r="T4" s="3"/>
       <c r="U4" s="3" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="V4" s="3" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="W4" s="9" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="X4" s="3"/>
       <c r="Y4" s="1" t="s">
@@ -2118,7 +2576,7 @@
       </c>
       <c r="AG4" s="3"/>
       <c r="AH4" s="1" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="AI4" s="3"/>
       <c r="AJ4" s="3"/>
@@ -2134,11 +2592,11 @@
         <v>32</v>
       </c>
       <c r="AT4" s="3" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="AU4" s="3"/>
       <c r="AV4" s="1" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="AW4" s="3"/>
       <c r="AX4" s="3"/>

--- a/LangMod/EN/SmallResource.xlsx
+++ b/LangMod/EN/SmallResource.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="152">
   <si>
     <t>id</t>
   </si>
@@ -117,6 +117,33 @@
     <t>fragment_small</t>
   </si>
   <si>
+    <t>6491200</t>
+  </si>
+  <si>
+    <t>Butcher</t>
+  </si>
+  <si>
+    <t>6491201</t>
+  </si>
+  <si>
+    <t>6491202</t>
+  </si>
+  <si>
+    <t>6491203</t>
+  </si>
+  <si>
+    <t>6491204</t>
+  </si>
+  <si>
+    <t>figure</t>
+  </si>
+  <si>
+    <t>6491205</t>
+  </si>
+  <si>
+    <t>figure2</t>
+  </si>
+  <si>
     <t>name_JP</t>
   </si>
   <si>
@@ -360,19 +387,19 @@
     <t>granite</t>
   </si>
   <si>
+    <t>logSmall</t>
+  </si>
+  <si>
+    <t>小さな丸太(Old)</t>
+  </si>
+  <si>
+    <t>small log(Old)</t>
+  </si>
+  <si>
     <t>※このアイテムは将来のアプデで無効化されます。加工する事で有効なアイテムに変換できます。</t>
   </si>
   <si>
     <t>*This item will be disabled in a future update. You can convert it into a usable item by processing it.</t>
-  </si>
-  <si>
-    <t>logSmall</t>
-  </si>
-  <si>
-    <t>小さな丸太(Old)</t>
-  </si>
-  <si>
-    <t>small log(Old)</t>
   </si>
   <si>
     <t>claySmall</t>
@@ -507,7 +534,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -540,6 +567,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
@@ -788,13 +818,13 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="7.88"/>
-    <col customWidth="1" min="2" max="2" width="9.75"/>
+    <col customWidth="1" min="2" max="2" width="11.5"/>
     <col customWidth="1" min="3" max="3" width="8.38"/>
     <col customWidth="1" min="4" max="4" width="7.5"/>
     <col customWidth="1" min="5" max="5" width="5.0"/>
     <col customWidth="1" min="6" max="6" width="3.0"/>
     <col customWidth="1" min="7" max="7" width="3.88"/>
-    <col customWidth="1" min="9" max="9" width="6.0"/>
+    <col customWidth="1" min="9" max="9" width="12.88"/>
     <col customWidth="1" min="10" max="10" width="6.13"/>
     <col customWidth="1" min="11" max="11" width="5.88"/>
   </cols>
@@ -911,7 +941,7 @@
     </row>
     <row r="3">
       <c r="A3" s="4">
-        <f>MAX(A4:A1083)</f>
+        <f>MAX(A4:A1089)</f>
         <v>0</v>
       </c>
       <c r="B3" s="5"/>
@@ -1109,7 +1139,9 @@
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
+      <c r="K7" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
@@ -1132,17 +1164,29 @@
       <c r="AE7" s="3"/>
     </row>
     <row r="8">
-      <c r="A8" s="8"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="9"/>
+      <c r="A8" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
-      <c r="H8" s="10"/>
+      <c r="H8" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
+      <c r="K8" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
@@ -1164,6 +1208,323 @@
       <c r="AD8" s="1"/>
       <c r="AE8" s="1"/>
     </row>
+    <row r="9">
+      <c r="A9" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1"/>
+      <c r="U9" s="1"/>
+      <c r="V9" s="1"/>
+      <c r="W9" s="1"/>
+      <c r="X9" s="1"/>
+      <c r="Y9" s="1"/>
+      <c r="Z9" s="1"/>
+      <c r="AA9" s="1"/>
+      <c r="AB9" s="1"/>
+      <c r="AC9" s="1"/>
+      <c r="AD9" s="1"/>
+      <c r="AE9" s="1"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
+      <c r="Q10" s="1"/>
+      <c r="R10" s="1"/>
+      <c r="S10" s="1"/>
+      <c r="T10" s="1"/>
+      <c r="U10" s="1"/>
+      <c r="V10" s="1"/>
+      <c r="W10" s="1"/>
+      <c r="X10" s="1"/>
+      <c r="Y10" s="1"/>
+      <c r="Z10" s="1"/>
+      <c r="AA10" s="1"/>
+      <c r="AB10" s="1"/>
+      <c r="AC10" s="1"/>
+      <c r="AD10" s="1"/>
+      <c r="AE10" s="1"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+      <c r="U11" s="1"/>
+      <c r="V11" s="1"/>
+      <c r="W11" s="1"/>
+      <c r="X11" s="1"/>
+      <c r="Y11" s="1"/>
+      <c r="Z11" s="1"/>
+      <c r="AA11" s="1"/>
+      <c r="AB11" s="1"/>
+      <c r="AC11" s="1"/>
+      <c r="AD11" s="1"/>
+      <c r="AE11" s="1"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
+      <c r="R12" s="1"/>
+      <c r="S12" s="1"/>
+      <c r="T12" s="1"/>
+      <c r="U12" s="1"/>
+      <c r="V12" s="1"/>
+      <c r="W12" s="1"/>
+      <c r="X12" s="1"/>
+      <c r="Y12" s="1"/>
+      <c r="Z12" s="1"/>
+      <c r="AA12" s="1"/>
+      <c r="AB12" s="1"/>
+      <c r="AC12" s="1"/>
+      <c r="AD12" s="1"/>
+      <c r="AE12" s="1"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
+      <c r="R13" s="1"/>
+      <c r="S13" s="1"/>
+      <c r="T13" s="1"/>
+      <c r="U13" s="1"/>
+      <c r="V13" s="1"/>
+      <c r="W13" s="1"/>
+      <c r="X13" s="1"/>
+      <c r="Y13" s="1"/>
+      <c r="Z13" s="1"/>
+      <c r="AA13" s="1"/>
+      <c r="AB13" s="1"/>
+      <c r="AC13" s="1"/>
+      <c r="AD13" s="1"/>
+      <c r="AE13" s="1"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="8"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1"/>
+      <c r="S14" s="1"/>
+      <c r="T14" s="1"/>
+      <c r="U14" s="1"/>
+      <c r="V14" s="1"/>
+      <c r="W14" s="1"/>
+      <c r="X14" s="1"/>
+      <c r="Y14" s="1"/>
+      <c r="Z14" s="1"/>
+      <c r="AA14" s="1"/>
+      <c r="AB14" s="1"/>
+      <c r="AC14" s="1"/>
+      <c r="AD14" s="1"/>
+      <c r="AE14" s="1"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="8"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
+      <c r="S15" s="1"/>
+      <c r="T15" s="1"/>
+      <c r="U15" s="1"/>
+      <c r="V15" s="1"/>
+      <c r="W15" s="1"/>
+      <c r="X15" s="1"/>
+      <c r="Y15" s="1"/>
+      <c r="Z15" s="1"/>
+      <c r="AA15" s="1"/>
+      <c r="AB15" s="1"/>
+      <c r="AC15" s="1"/>
+      <c r="AD15" s="1"/>
+      <c r="AE15" s="1"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="8"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -1180,25 +1541,25 @@
     <col customWidth="1" min="3" max="3" width="4.88"/>
     <col customWidth="1" min="4" max="4" width="6.38"/>
     <col customWidth="1" min="5" max="5" width="2.88"/>
-    <col customWidth="1" min="7" max="7" width="5.0"/>
-    <col customWidth="1" min="8" max="8" width="4.88"/>
+    <col customWidth="1" min="7" max="7" width="2.38"/>
+    <col customWidth="1" min="8" max="8" width="2.75"/>
     <col customWidth="1" min="9" max="9" width="8.63"/>
     <col customWidth="1" min="10" max="10" width="14.88"/>
     <col customWidth="1" min="11" max="11" width="4.13"/>
-    <col customWidth="1" min="12" max="12" width="5.25"/>
-    <col customWidth="1" min="14" max="14" width="7.5"/>
+    <col customWidth="1" min="12" max="12" width="2.75"/>
+    <col customWidth="1" min="14" max="14" width="3.88"/>
     <col customWidth="1" min="15" max="15" width="3.75"/>
     <col customWidth="1" min="16" max="16" width="3.63"/>
     <col customWidth="1" min="17" max="17" width="3.5"/>
     <col customWidth="1" min="18" max="18" width="3.88"/>
-    <col customWidth="1" min="19" max="19" width="7.75"/>
-    <col customWidth="1" min="20" max="20" width="5.25"/>
-    <col customWidth="1" min="21" max="21" width="6.13"/>
-    <col customWidth="1" min="22" max="22" width="5.88"/>
-    <col customWidth="1" min="23" max="23" width="25.0"/>
-    <col customWidth="1" min="24" max="24" width="10.13"/>
+    <col customWidth="1" min="19" max="19" width="3.63"/>
+    <col customWidth="1" min="20" max="20" width="2.0"/>
+    <col customWidth="1" min="21" max="21" width="2.5"/>
+    <col customWidth="1" min="22" max="22" width="2.13"/>
+    <col customWidth="1" min="23" max="23" width="10.13"/>
+    <col customWidth="1" min="24" max="24" width="2.38"/>
     <col customWidth="1" min="25" max="25" width="6.38"/>
-    <col customWidth="1" min="26" max="26" width="5.0"/>
+    <col customWidth="1" min="26" max="26" width="1.63"/>
     <col customWidth="1" min="27" max="27" width="5.38"/>
     <col customWidth="1" min="28" max="28" width="3.0"/>
     <col customWidth="1" min="29" max="29" width="6.25"/>
@@ -1229,157 +1590,157 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="V1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="Z1" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="AA1" s="11" t="s">
-        <v>57</v>
+        <v>65</v>
+      </c>
+      <c r="AA1" s="12" t="s">
+        <v>66</v>
       </c>
       <c r="AB1" s="3" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="AC1" s="3" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="AD1" s="3" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="AE1" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="AF1" s="11" t="s">
-        <v>62</v>
+        <v>70</v>
+      </c>
+      <c r="AF1" s="12" t="s">
+        <v>71</v>
       </c>
       <c r="AG1" s="3" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="AH1" s="3" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="AI1" s="3" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="AJ1" s="3" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="AK1" s="3" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="AL1" s="3" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="AM1" s="3" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="AN1" s="3" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="AO1" s="3" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="AP1" s="3" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="AQ1" s="3" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="AR1" s="3" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AS1" s="3" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AT1" s="1" t="s">
         <v>10</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AW1" s="3" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AX1" s="3" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="BA1" s="3"/>
       <c r="BB1" s="3"/>
@@ -1441,19 +1802,19 @@
         <v>12</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>11</v>
@@ -1479,7 +1840,7 @@
       <c r="Z2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="AA2" s="11" t="s">
+      <c r="AA2" s="12" t="s">
         <v>11</v>
       </c>
       <c r="AB2" s="3" t="s">
@@ -1494,7 +1855,7 @@
       <c r="AE2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AF2" s="11" t="s">
+      <c r="AF2" s="12" t="s">
         <v>11</v>
       </c>
       <c r="AG2" s="3" t="s">
@@ -1504,7 +1865,7 @@
         <v>13</v>
       </c>
       <c r="AI2" s="3" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="AJ2" s="3" t="s">
         <v>11</v>
@@ -1513,13 +1874,13 @@
         <v>12</v>
       </c>
       <c r="AL2" s="3" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AM2" s="3" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AN2" s="3" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AO2" s="3" t="s">
         <v>12</v>
@@ -1583,18 +1944,18 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="7" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="7" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="J3" s="3"/>
       <c r="K3" s="7" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
@@ -1612,27 +1973,27 @@
       <c r="U3" s="3"/>
       <c r="V3" s="3"/>
       <c r="W3" s="4" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="X3" s="3"/>
       <c r="Y3" s="7" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="Z3" s="3"/>
-      <c r="AA3" s="12">
+      <c r="AA3" s="13">
         <v>100.0</v>
       </c>
-      <c r="AB3" s="13">
+      <c r="AB3" s="14">
         <v>1.0</v>
       </c>
       <c r="AC3" s="7" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="AD3" s="3"/>
       <c r="AE3" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="AF3" s="12">
+        <v>94</v>
+      </c>
+      <c r="AF3" s="13">
         <v>1000.0</v>
       </c>
       <c r="AG3" s="3"/>
@@ -1683,30 +2044,30 @@
         <v>21</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="1" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="10" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="N4" s="10"/>
       <c r="O4" s="3"/>
@@ -1718,26 +2079,26 @@
       <c r="U4" s="3"/>
       <c r="V4" s="3"/>
       <c r="W4" s="10" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
-      <c r="AA4" s="14">
+      <c r="AA4" s="15">
         <v>30.0</v>
       </c>
-      <c r="AB4" s="15">
+      <c r="AB4" s="16">
         <v>1.0</v>
       </c>
       <c r="AC4" s="3"/>
       <c r="AD4" s="3"/>
       <c r="AE4" s="3"/>
-      <c r="AF4" s="14">
+      <c r="AF4" s="15">
         <v>600.0</v>
       </c>
       <c r="AG4" s="3"/>
       <c r="AH4" s="3" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="AI4" s="3"/>
       <c r="AJ4" s="3"/>
@@ -1783,28 +2144,28 @@
         <v>30</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="1" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="I5" s="1" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="10" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="N5" s="10"/>
       <c r="O5" s="3"/>
@@ -1816,23 +2177,23 @@
       <c r="U5" s="3"/>
       <c r="V5" s="3"/>
       <c r="W5" s="1" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="X5" s="3"/>
       <c r="Y5" s="1" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="Z5" s="3"/>
-      <c r="AA5" s="14">
+      <c r="AA5" s="15">
         <v>70.0</v>
       </c>
-      <c r="AB5" s="15">
+      <c r="AB5" s="16">
         <v>4.0</v>
       </c>
       <c r="AC5" s="3"/>
       <c r="AD5" s="3"/>
       <c r="AE5" s="3"/>
-      <c r="AF5" s="14">
+      <c r="AF5" s="15">
         <v>90.0</v>
       </c>
       <c r="AG5" s="3"/>
@@ -1881,28 +2242,28 @@
         <v>33</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="1" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
       <c r="I6" s="1" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="10" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="N6" s="10"/>
       <c r="O6" s="3"/>
@@ -1914,28 +2275,28 @@
       <c r="U6" s="3"/>
       <c r="V6" s="3"/>
       <c r="W6" s="1" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="X6" s="3"/>
       <c r="Y6" s="1" t="s">
         <v>32</v>
       </c>
       <c r="Z6" s="3"/>
-      <c r="AA6" s="14">
+      <c r="AA6" s="15">
         <v>10.0</v>
       </c>
-      <c r="AB6" s="15">
+      <c r="AB6" s="16">
         <v>1.0</v>
       </c>
       <c r="AC6" s="3"/>
       <c r="AD6" s="3"/>
       <c r="AE6" s="3"/>
-      <c r="AF6" s="14">
+      <c r="AF6" s="15">
         <v>60.0</v>
       </c>
       <c r="AG6" s="3"/>
       <c r="AH6" s="3" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="AI6" s="3"/>
       <c r="AJ6" s="3"/>
@@ -1983,28 +2344,28 @@
         <v>26</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="1" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="I7" s="1" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="10" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="N7" s="1"/>
       <c r="O7" s="3"/>
@@ -2016,28 +2377,28 @@
       <c r="U7" s="3"/>
       <c r="V7" s="3"/>
       <c r="W7" s="10" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="X7" s="3"/>
       <c r="Y7" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="Z7" s="3"/>
-      <c r="AA7" s="14">
+      <c r="AA7" s="15">
         <v>25.0</v>
       </c>
-      <c r="AB7" s="15">
+      <c r="AB7" s="16">
         <v>1.0</v>
       </c>
       <c r="AC7" s="3"/>
       <c r="AD7" s="3"/>
       <c r="AE7" s="3"/>
-      <c r="AF7" s="14">
+      <c r="AF7" s="15">
         <v>500.0</v>
       </c>
       <c r="AG7" s="3"/>
       <c r="AH7" s="3" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="AI7" s="3"/>
       <c r="AJ7" s="3"/>
@@ -2055,12 +2416,6 @@
       <c r="AV7" s="1"/>
       <c r="AW7" s="3"/>
       <c r="AX7" s="3"/>
-      <c r="AY7" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="AZ7" s="9" t="s">
-        <v>116</v>
-      </c>
       <c r="BA7" s="3"/>
       <c r="BB7" s="3"/>
       <c r="BC7" s="3"/>
@@ -2084,33 +2439,33 @@
     </row>
     <row r="8">
       <c r="A8" s="10" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="I8" s="1" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="10" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="N8" s="10"/>
       <c r="O8" s="3"/>
@@ -2122,26 +2477,26 @@
       <c r="U8" s="3"/>
       <c r="V8" s="3"/>
       <c r="W8" s="10" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="X8" s="3"/>
       <c r="Y8" s="3"/>
       <c r="Z8" s="3"/>
-      <c r="AA8" s="14">
+      <c r="AA8" s="15">
         <v>30.0</v>
       </c>
-      <c r="AB8" s="15">
+      <c r="AB8" s="16">
         <v>1.0</v>
       </c>
       <c r="AC8" s="3"/>
       <c r="AD8" s="3"/>
       <c r="AE8" s="3"/>
-      <c r="AF8" s="14">
+      <c r="AF8" s="15">
         <v>600.0</v>
       </c>
       <c r="AG8" s="3"/>
       <c r="AH8" s="3" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="AI8" s="3"/>
       <c r="AJ8" s="3"/>
@@ -2160,10 +2515,10 @@
       <c r="AW8" s="3"/>
       <c r="AX8" s="3"/>
       <c r="AY8" s="9" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="AZ8" s="9" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="BA8" s="3"/>
       <c r="BB8" s="3"/>
@@ -2188,31 +2543,31 @@
     </row>
     <row r="9">
       <c r="A9" s="10" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
       <c r="E9" s="1" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="I9" s="1" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="10" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="N9" s="10"/>
       <c r="O9" s="3"/>
@@ -2224,23 +2579,23 @@
       <c r="U9" s="3"/>
       <c r="V9" s="3"/>
       <c r="W9" s="1" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="X9" s="3"/>
       <c r="Y9" s="1" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="Z9" s="3"/>
-      <c r="AA9" s="14">
+      <c r="AA9" s="15">
         <v>70.0</v>
       </c>
-      <c r="AB9" s="15">
+      <c r="AB9" s="16">
         <v>4.0</v>
       </c>
       <c r="AC9" s="3"/>
       <c r="AD9" s="3"/>
       <c r="AE9" s="3"/>
-      <c r="AF9" s="14">
+      <c r="AF9" s="15">
         <v>90.0</v>
       </c>
       <c r="AG9" s="3"/>
@@ -2262,10 +2617,10 @@
       <c r="AW9" s="3"/>
       <c r="AX9" s="3"/>
       <c r="AY9" s="9" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="AZ9" s="9" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="BA9" s="3"/>
       <c r="BB9" s="3"/>
@@ -2290,31 +2645,31 @@
     </row>
     <row r="10">
       <c r="A10" s="10" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="1" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="I10" s="1" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="10" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="N10" s="10"/>
       <c r="O10" s="3"/>
@@ -2326,28 +2681,28 @@
       <c r="U10" s="3"/>
       <c r="V10" s="3"/>
       <c r="W10" s="1" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="X10" s="3"/>
       <c r="Y10" s="1" t="s">
         <v>32</v>
       </c>
       <c r="Z10" s="3"/>
-      <c r="AA10" s="14">
+      <c r="AA10" s="15">
         <v>10.0</v>
       </c>
-      <c r="AB10" s="15">
+      <c r="AB10" s="16">
         <v>1.0</v>
       </c>
       <c r="AC10" s="3"/>
       <c r="AD10" s="3"/>
       <c r="AE10" s="3"/>
-      <c r="AF10" s="14">
+      <c r="AF10" s="15">
         <v>60.0</v>
       </c>
       <c r="AG10" s="3"/>
       <c r="AH10" s="3" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="AI10" s="3"/>
       <c r="AJ10" s="3"/>
@@ -2368,10 +2723,10 @@
       <c r="AW10" s="3"/>
       <c r="AX10" s="3"/>
       <c r="AY10" s="9" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="AZ10" s="9" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="BA10" s="3"/>
       <c r="BB10" s="3"/>
@@ -2396,31 +2751,31 @@
     </row>
     <row r="11">
       <c r="A11" s="10" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="1" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="1" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="10" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="N11" s="1"/>
       <c r="O11" s="3"/>
@@ -2432,28 +2787,28 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="10" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="X11" s="3"/>
       <c r="Y11" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="Z11" s="3"/>
-      <c r="AA11" s="14">
+      <c r="AA11" s="15">
         <v>25.0</v>
       </c>
-      <c r="AB11" s="15">
+      <c r="AB11" s="16">
         <v>1.0</v>
       </c>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-      <c r="AF11" s="14">
+      <c r="AF11" s="15">
         <v>500.0</v>
       </c>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
@@ -2471,8 +2826,12 @@
       <c r="AV11" s="1"/>
       <c r="AW11" s="3"/>
       <c r="AX11" s="3"/>
-      <c r="AY11" s="3"/>
-      <c r="AZ11" s="3"/>
+      <c r="AY11" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="AZ11" s="9" t="s">
+        <v>128</v>
+      </c>
       <c r="BA11" s="3"/>
       <c r="BB11" s="3"/>
       <c r="BC11" s="3"/>
@@ -2507,40 +2866,40 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="16" t="s">
-        <v>129</v>
+      <c r="A1" s="17" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="1" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="1" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="1" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
@@ -2549,34 +2908,34 @@
       <c r="S4" s="3"/>
       <c r="T4" s="3"/>
       <c r="U4" s="3" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="V4" s="3" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="W4" s="9" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="X4" s="3"/>
       <c r="Y4" s="1" t="s">
         <v>32</v>
       </c>
       <c r="Z4" s="3"/>
-      <c r="AA4" s="17">
+      <c r="AA4" s="18">
         <v>50.0</v>
       </c>
-      <c r="AB4" s="15">
+      <c r="AB4" s="16">
         <v>3.0</v>
       </c>
       <c r="AC4" s="3"/>
       <c r="AD4" s="3"/>
       <c r="AE4" s="3"/>
-      <c r="AF4" s="17">
+      <c r="AF4" s="18">
         <v>10.0</v>
       </c>
       <c r="AG4" s="3"/>
       <c r="AH4" s="1" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="AI4" s="3"/>
       <c r="AJ4" s="3"/>
@@ -2592,11 +2951,11 @@
         <v>32</v>
       </c>
       <c r="AT4" s="3" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="AU4" s="3"/>
       <c r="AV4" s="1" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="AW4" s="3"/>
       <c r="AX4" s="3"/>
